--- a/out/Te_P_PbCl__pre.xlsx
+++ b/out/Te_P_PbCl__pre.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="predictions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics_thr_0.36" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metrics_thr_0.35" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +518,7 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>y_pred_thr_0.36</t>
+          <t>y_pred_thr_0.35</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2927,7 @@
         <v>0.3589323461055756</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -4350,4 +4351,134 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TPR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>FNR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>TNR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>FPR</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PPV</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>NPV</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>FOR</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8927875243664717</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9411764705882353</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>